--- a/Dictionary.xlsx
+++ b/Dictionary.xlsx
@@ -18,7 +18,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,12 +48,6 @@
       <name val="Times New Roman"/>
       <family val="1"/>
       <color rgb="FFC00000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <color rgb="FFFF0000"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -734,7 +728,8 @@
   <cols>
     <col width="39.6640625" customWidth="1" style="7" min="1" max="3"/>
     <col width="39.6640625" customWidth="1" style="11" min="4" max="4"/>
-    <col width="8.88671875" customWidth="1" style="9" min="5" max="16384"/>
+    <col width="8.88671875" customWidth="1" style="9" min="5" max="5"/>
+    <col width="8.88671875" customWidth="1" style="9" min="6" max="16384"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -760,18 +755,10 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="inlineStr">
-        <is>
-          <t>từ ngày 04 tháng 11 năm 2025 đến ngày 31 tháng 12 năm 2025</t>
-        </is>
-      </c>
+      <c r="A2" s="18" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="19" t="inlineStr">
-        <is>
-          <t>Từ 04/11/2025 đến 31/12/2025</t>
-        </is>
-      </c>
+      <c r="A3" s="19" t="inlineStr"/>
     </row>
     <row r="5" customFormat="1" s="5">
       <c r="A5" s="1" t="inlineStr">
@@ -1076,8 +1063,8 @@
         <v/>
       </c>
     </row>
-    <row r="19" customFormat="1" s="12">
-      <c r="A19" s="10" t="inlineStr"/>
+    <row r="19" ht="27.6" customFormat="1" customHeight="1" s="12">
+      <c r="A19" s="10" t="n"/>
       <c r="B19" s="6" t="inlineStr">
         <is>
           <t>From November 04, 2025 to December 31, 2025</t>
@@ -1162,17 +1149,17 @@
     <row r="23" ht="41.4" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Cho giai đoạn từ ngày 04 tháng 11 năm 2025 đến ngày 31 tháng 12 năm 2025</t>
+          <t xml:space="preserve">Cho giai đoạn </t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>For the period from November 04, 2025 to December 31, 2025</t>
+          <t xml:space="preserve">For the period from  to </t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>2025年11月04日至2025年12月31日期间</t>
+          <t>至期间</t>
         </is>
       </c>
       <c r="D23" s="6">
@@ -1183,12 +1170,12 @@
     <row r="24" ht="41.4" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Cho giai đoạn 04/11/2025 đến 31/12/2025</t>
+          <t xml:space="preserve">Cho giai đoạn  đến </t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>For the period from November 04, 2025 to December 31, 2025</t>
+          <t xml:space="preserve">For the period from  to </t>
         </is>
       </c>
       <c r="C24" s="6">
@@ -1203,12 +1190,12 @@
     <row r="25" ht="41.4" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>cho giai đoạn từ ngày 04 tháng 11 năm 2025 đến ngày 31 tháng 12 năm 2025</t>
+          <t xml:space="preserve">cho giai đoạn </t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>for the period from November 04, 2025 to December 31, 2025</t>
+          <t xml:space="preserve">for the period from  to </t>
         </is>
       </c>
       <c r="C25" s="6">
@@ -1223,12 +1210,12 @@
     <row r="26" ht="41.4" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>cho giai đoạn 04/11/2025 đến 31/12/2025</t>
+          <t xml:space="preserve">cho giai đoạn  đến </t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>for the period from November 04, 2025 to December 31, 2025</t>
+          <t xml:space="preserve">for the period from  to </t>
         </is>
       </c>
       <c r="C26" s="6">
@@ -1309,22 +1296,22 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>[ngàykếtthúcnăm]</t>
+          <t>[ngàybáocáo]</t>
         </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
-          <t>December 31, 2025</t>
+          <t>March 31, 2026</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>2025年12月31日</t>
+          <t>2026年03月31日</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>2025年12月31日</t>
+          <t>2026年03月31日</t>
         </is>
       </c>
     </row>
@@ -1353,22 +1340,22 @@
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>[ngàybáocáo]</t>
+          <t>[ngàykếtthúcnăm]</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>March 31, 2026</t>
+          <t>December 31, 2025</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>2026年03月31日</t>
+          <t>2025年12月31日</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>2026年03月31日</t>
+          <t>2025年12月31日</t>
         </is>
       </c>
     </row>
@@ -1397,12 +1384,12 @@
     <row r="34" ht="55.2" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>CHO GIAI ĐOẠN TỪ NGÀY 04 THÁNG 11 NĂM 2025 ĐẾN NGÀY 31 THÁNG 12 NĂM 2025</t>
+          <t xml:space="preserve">CHO GIAI ĐOẠN </t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>FOR THE PERIOD FROM NOVEMBER 04, 2025 TO DECEMBER 31, 2025</t>
+          <t xml:space="preserve">FOR THE PERIOD FROM  TO </t>
         </is>
       </c>
       <c r="C34" s="6">
@@ -1417,12 +1404,12 @@
     <row r="35" ht="41.4" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>CHO GIAI ĐOẠN TỪ 04/11/2025 ĐẾN 31/12/2025</t>
+          <t xml:space="preserve">CHO GIAI ĐOẠN </t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>FOR THE PERIOD FROM NOVEMBER 04, 2025 TO DECEMBER 31, 2025</t>
+          <t xml:space="preserve">FOR THE PERIOD FROM  TO </t>
         </is>
       </c>
       <c r="C35" s="6">
@@ -1462,7 +1449,7 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>The auditors, U&amp;I Auditing Company Limited, have performed audit on the Company’s financial statements for the period from November 04, 2025 to December 31, 2025 and have expressed their willingness to accept reappointment.</t>
+          <t>The auditors, U&amp;I Auditing Company Limited, have performed audit on the Company’s financial statements for the period from  to  and have expressed their willingness to accept reappointment.</t>
         </is>
       </c>
       <c r="C37" s="6">
@@ -1502,7 +1489,7 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corporate income tax expense for the period from November 04, 2025 to December 31, 2025 is calculated on the estimated assessable income. Corporate income tax expense will be determined again by the tax authority through their tax reviews. </t>
+          <t xml:space="preserve">Corporate income tax expense for the period from  to  is calculated on the estimated assessable income. Corporate income tax expense will be determined again by the tax authority through their tax reviews. </t>
         </is>
       </c>
       <c r="C39" s="6">
@@ -1539,29 +1526,29 @@
     <row r="41" ht="82.8" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>Do đó, không có chi phí thuế thu nhập doanh nghiệp hoãn lại được ghi nhận cho giai đoạn từ ngày 04 tháng 11 năm 2025 đến ngày 31 tháng 12 năm 2025.</t>
+          <t>Do đó, không có chi phí thuế thu nhập doanh nghiệp hoãn lại được ghi nhận cho giai đoạn .</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>Therefore, no deferred corporate income tax expense is provided in the period from November 04, 2025 to December 31, 2025</t>
+          <t xml:space="preserve">Therefore, no deferred corporate income tax expense is provided in the period from  to </t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>据此，并无递延所得税费用2025年11月04日至2025年12月31日期间内得以认列。</t>
+          <t>据此，并无递延所得税费用至期间内得以认列。</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>據此，並無遞延所得稅費用2025年11月04日至2025年12月31日期間內得以認列。</t>
+          <t>據此，並無遞延所得稅費用至期間內得以認列。</t>
         </is>
       </c>
     </row>
     <row r="42" ht="82.8" customHeight="1">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>Do đó, không có chi phí thuế thu nhập doanh nghiệp hoãn lại được ghi nhận trong giai đoạn từ ngày 04 tháng 11 năm 2025 đến ngày 31 tháng 12 năm 2025.</t>
+          <t>Do đó, không có chi phí thuế thu nhập doanh nghiệp hoãn lại được ghi nhận trong giai đoạn .</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
@@ -1608,7 +1595,7 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>In the period from November 04, 2025 to December 31, 2025, the Company entered into significant economic transactions with its related parties as shown in the following table:</t>
+          <t>In the period from  to , the Company entered into significant economic transactions with its related parties as shown in the following table:</t>
         </is>
       </c>
       <c r="C44" s="6">
@@ -1648,7 +1635,7 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>In the period from November 04, 2025 to December 31, 2025, the Company entered into significant economic transactions, receivables and payables with its related parties as shown in the following table</t>
+          <t>In the period from  to , the Company entered into significant economic transactions, receivables and payables with its related parties as shown in the following table</t>
         </is>
       </c>
       <c r="C46" s="6">
@@ -1688,7 +1675,7 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>In the period from November 04, 2025 to December 31, 2025, the Company had no significant economic transactions with its related parties.</t>
+          <t>In the period from  to , the Company had no significant economic transactions with its related parties.</t>
         </is>
       </c>
       <c r="C48" s="6">
@@ -1913,12 +1900,12 @@
     <row r="60" ht="96.59999999999999" customHeight="1">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>Công ty không lập dự phòng chi phí thuế thu nhập doanh nghiệp hiện hành vì Công ty không có thu nhập chịu thuế cho giai đoạn từ ngày 04 tháng 11 năm 2025 đến ngày 31 tháng 12 năm 2025.</t>
+          <t>Công ty không lập dự phòng chi phí thuế thu nhập doanh nghiệp hiện hành vì Công ty không có thu nhập chịu thuế cho giai đoạn .</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>No provision for current corporate income tax expense has been provided as the Company has no taxable income arising in the period from November 04, 2025 to December 31, 2025</t>
+          <t xml:space="preserve">No provision for current corporate income tax expense has been provided as the Company has no taxable income arising in the period from  to </t>
         </is>
       </c>
       <c r="C60" s="6">
@@ -1933,7 +1920,7 @@
     <row r="61" ht="96.59999999999999" customHeight="1">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>Công ty không lập dự phòng chi phí thuế thu nhập doanh nghiệp hiện hành vì Công ty không có thu nhập chịu thuế trong giai đoạn từ ngày 04 tháng 11 năm 2025 đến ngày 31 tháng 12 năm 2025.</t>
+          <t>Công ty không lập dự phòng chi phí thuế thu nhập doanh nghiệp hiện hành vì Công ty không có thu nhập chịu thuế trong giai đoạn .</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
@@ -1975,12 +1962,12 @@
     <row r="63" ht="110.4" customHeight="1">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>Công ty không lập dự phòng chi phí thuế thu nhập doanh nghiệp hiện hành vì Công ty không có thu nhập tính thuế sau khi trừ chuyển lỗ cho giai đoạn từ ngày 04 tháng 11 năm 2025 đến ngày 31 tháng 12 năm 2025.</t>
+          <t>Công ty không lập dự phòng chi phí thuế thu nhập doanh nghiệp hiện hành vì Công ty không có thu nhập tính thuế sau khi trừ chuyển lỗ cho giai đoạn .</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>No provision for current corporate income tax expense has been provided as the Company has no assessable income after deducting tax loss brought forward in the period from November 04, 2025 to December 31, 2025</t>
+          <t xml:space="preserve">No provision for current corporate income tax expense has been provided as the Company has no assessable income after deducting tax loss brought forward in the period from  to </t>
         </is>
       </c>
       <c r="C63" s="6">

--- a/Dictionary.xlsx
+++ b/Dictionary.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0c0472821c82c727/Máy tính/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\AI\Python\11_Project\Translation_Tool\Translation_Tool_Antigravity_V5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{2CC533DB-1B09-44D2-BA33-2EE6C17287E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{849C8419-D54D-4302-A820-79F0EE1A6237}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFC475AB-5600-4860-9885-F1E3F9B628D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{63FBA5CB-1D78-4035-BA50-2E0EBEEEE1C5}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8052" uniqueCount="7024">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8055" uniqueCount="7025">
   <si>
     <t>Vietnamese</t>
   </si>
@@ -20859,9 +20859,6 @@
     <t>Từ [p1_day]/[p1_month]/[p1_year] đến [p2_day]/[p2_month]/[p2_year]</t>
   </si>
   <si>
-    <t>From Mar [p1_day], [p1_year] to Apr [p2_day], [p2_year]</t>
-  </si>
-  <si>
     <t>自[p1_year]/[p1_month]/[p1_day]日至[p2_year]/[p2_month]/[p2_day]日</t>
   </si>
   <si>
@@ -21112,6 +21109,12 @@
   </si>
   <si>
     <t>xyâ</t>
+  </si>
+  <si>
+    <t>new</t>
+  </si>
+  <si>
+    <t>From [p1_month] [p1_day], [p1_year] to [p2_month] [p2_day], [p2_year]</t>
   </si>
 </sst>
 </file>
@@ -21745,7 +21748,7 @@
         <v>6854</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>6977</v>
+        <v>6976</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>6855</v>
@@ -21759,7 +21762,7 @@
         <v>6928</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>7000</v>
+        <v>6999</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>6929</v>
@@ -21773,7 +21776,7 @@
         <v>6931</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>7000</v>
+        <v>6999</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>6929</v>
@@ -21784,10 +21787,10 @@
     </row>
     <row r="6" spans="1:4" ht="151.80000000000001" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>7022</v>
+        <v>7021</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>6978</v>
+        <v>6977</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>6857</v>
@@ -21801,7 +21804,7 @@
         <v>6932</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>7001</v>
+        <v>7000</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>6933</v>
@@ -21829,7 +21832,7 @@
         <v>6859</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>6979</v>
+        <v>6978</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>6860</v>
@@ -21843,7 +21846,7 @@
         <v>6861</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>6979</v>
+        <v>6978</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>6860</v>
@@ -21857,7 +21860,7 @@
         <v>6862</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>7014</v>
+        <v>7013</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>6860</v>
@@ -21871,7 +21874,7 @@
         <v>6935</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>7002</v>
+        <v>7001</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>6936</v>
@@ -21885,7 +21888,7 @@
         <v>6937</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>7002</v>
+        <v>7001</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>6936</v>
@@ -21899,27 +21902,27 @@
         <v>6938</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>7024</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>6939</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>6940</v>
-      </c>
       <c r="D14" s="2" t="s">
-        <v>6940</v>
+        <v>6939</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
+        <v>6974</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>7012</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>6975</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>7013</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>6976</v>
-      </c>
       <c r="D15" s="2" t="s">
-        <v>6976</v>
+        <v>6975</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="27.6" x14ac:dyDescent="0.3">
@@ -21927,7 +21930,7 @@
         <v>6863</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>6980</v>
+        <v>6979</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>6864</v>
@@ -21941,7 +21944,7 @@
         <v>6866</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>6981</v>
+        <v>6980</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>6867</v>
@@ -21955,7 +21958,7 @@
         <v>6869</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>6982</v>
+        <v>6981</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>6867</v>
@@ -21966,58 +21969,58 @@
     </row>
     <row r="19" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
+        <v>6940</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>7002</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>6941</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>7003</v>
-      </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="2" t="s">
         <v>6942</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>6943</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>6944</v>
+        <v>6943</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>7003</v>
+        <v>7002</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>6941</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>6942</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>6943</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>6945</v>
+        <v>6944</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>7004</v>
+        <v>7003</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>6941</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>6942</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>6943</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>6946</v>
+        <v>6945</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>7004</v>
+        <v>7003</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>6941</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>6942</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>6943</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -22025,7 +22028,7 @@
         <v>6899</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>6989</v>
+        <v>6988</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>6900</v>
@@ -22039,7 +22042,7 @@
         <v>6901</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>6989</v>
+        <v>6988</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>6900</v>
@@ -22067,7 +22070,7 @@
         <v>7</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>6979</v>
+        <v>6978</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>6860</v>
@@ -22095,7 +22098,7 @@
         <v>9</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>6989</v>
+        <v>6988</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>6900</v>
@@ -22109,7 +22112,7 @@
         <v>6870</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>7015</v>
+        <v>7014</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>6867</v>
@@ -22120,38 +22123,38 @@
     </row>
     <row r="30" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>6947</v>
+        <v>6946</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>7016</v>
+        <v>7015</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>6941</v>
+      </c>
+      <c r="D30" s="2" t="s">
         <v>6942</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>6943</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>6948</v>
+        <v>6947</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>7016</v>
+        <v>7015</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>6941</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>6942</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>6943</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="69" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:4" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>6871</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>6983</v>
+        <v>6982</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>6872</v>
@@ -22162,16 +22165,16 @@
     </row>
     <row r="33" spans="1:4" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
+        <v>6948</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>7004</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>6949</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>7005</v>
-      </c>
-      <c r="C33" s="2" t="s">
+      <c r="D33" s="2" t="s">
         <v>6950</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>6951</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="82.8" x14ac:dyDescent="0.3">
@@ -22179,7 +22182,7 @@
         <v>6874</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>6984</v>
+        <v>6983</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>6875</v>
@@ -22190,16 +22193,16 @@
     </row>
     <row r="35" spans="1:4" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
+        <v>6951</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>7005</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>6952</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>7006</v>
-      </c>
-      <c r="C35" s="2" t="s">
+      <c r="D35" s="2" t="s">
         <v>6953</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>6954</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
@@ -22218,30 +22221,30 @@
     </row>
     <row r="37" spans="1:4" ht="69" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
+        <v>6954</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>7006</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>6955</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>7007</v>
-      </c>
-      <c r="C37" s="2" t="s">
+      <c r="D37" s="2" t="s">
         <v>6956</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>6957</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="69" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>6958</v>
+        <v>6957</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>7007</v>
+        <v>7006</v>
       </c>
       <c r="C38" s="2" t="s">
+        <v>6955</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>6956</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>6957</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
@@ -22249,7 +22252,7 @@
         <v>6881</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>6985</v>
+        <v>6984</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>6882</v>
@@ -22260,16 +22263,16 @@
     </row>
     <row r="40" spans="1:4" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
+        <v>6958</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>7007</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>6959</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>7008</v>
-      </c>
-      <c r="C40" s="2" t="s">
+      <c r="D40" s="2" t="s">
         <v>6960</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>6961</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="69" x14ac:dyDescent="0.3">
@@ -22277,7 +22280,7 @@
         <v>6884</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>6986</v>
+        <v>6985</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>6885</v>
@@ -22288,16 +22291,16 @@
     </row>
     <row r="42" spans="1:4" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
+        <v>6961</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>7008</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>6962</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>7009</v>
-      </c>
-      <c r="C42" s="2" t="s">
+      <c r="D42" s="2" t="s">
         <v>6963</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>6964</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
@@ -22305,7 +22308,7 @@
         <v>6887</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>6987</v>
+        <v>6986</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>6888</v>
@@ -22316,16 +22319,16 @@
     </row>
     <row r="44" spans="1:4" ht="69" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
+        <v>6964</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>7009</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>6965</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>7010</v>
-      </c>
-      <c r="C44" s="2" t="s">
+      <c r="D44" s="2" t="s">
         <v>6966</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>6967</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
@@ -22333,7 +22336,7 @@
         <v>6902</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>6990</v>
+        <v>6989</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>6903</v>
@@ -22347,7 +22350,7 @@
         <v>6905</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>6991</v>
+        <v>6990</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>6906</v>
@@ -22361,7 +22364,7 @@
         <v>6908</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>6992</v>
+        <v>6991</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>6909</v>
@@ -22375,7 +22378,7 @@
         <v>6911</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>6993</v>
+        <v>6992</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>6912</v>
@@ -22389,7 +22392,7 @@
         <v>6914</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>6994</v>
+        <v>6993</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>6906</v>
@@ -22403,7 +22406,7 @@
         <v>6915</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>6995</v>
+        <v>6994</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>6916</v>
@@ -22417,7 +22420,7 @@
         <v>6918</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>6996</v>
+        <v>6995</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>6919</v>
@@ -22431,7 +22434,7 @@
         <v>6921</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>6997</v>
+        <v>6996</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>6922</v>
@@ -22445,7 +22448,7 @@
         <v>6924</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>6998</v>
+        <v>6997</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>6916</v>
@@ -22459,7 +22462,7 @@
         <v>6925</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>6999</v>
+        <v>6998</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>6926</v>
@@ -22484,30 +22487,30 @@
     </row>
     <row r="56" spans="1:4" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
+        <v>6967</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>7010</v>
+      </c>
+      <c r="C56" s="2" t="s">
         <v>6968</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>7011</v>
-      </c>
-      <c r="C56" s="2" t="s">
+      <c r="D56" s="2" t="s">
         <v>6969</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>6970</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>6971</v>
+        <v>6970</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>7011</v>
+        <v>7010</v>
       </c>
       <c r="C57" s="2" t="s">
+        <v>6968</v>
+      </c>
+      <c r="D57" s="2" t="s">
         <v>6969</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>6970</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
@@ -22526,16 +22529,16 @@
     </row>
     <row r="59" spans="1:4" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
+        <v>6971</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>7011</v>
+      </c>
+      <c r="C59" s="2" t="s">
         <v>6972</v>
       </c>
-      <c r="B59" s="2" t="s">
-        <v>7012</v>
-      </c>
-      <c r="C59" s="2" t="s">
+      <c r="D59" s="2" t="s">
         <v>6973</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>6974</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
@@ -22543,7 +22546,7 @@
         <v>6896</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>6988</v>
+        <v>6987</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>6897</v>
@@ -26562,7 +26565,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="348" spans="1:4" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:4" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A348" s="2" t="s">
         <v>965</v>
       </c>
@@ -28760,7 +28763,7 @@
         <v>1543</v>
       </c>
     </row>
-    <row r="505" spans="1:4" ht="138" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:4" ht="151.80000000000001" x14ac:dyDescent="0.3">
       <c r="A505" s="2" t="s">
         <v>1544</v>
       </c>
@@ -29068,7 +29071,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="527" spans="1:4" ht="138" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:4" ht="151.80000000000001" x14ac:dyDescent="0.3">
       <c r="A527" s="2" t="s">
         <v>1619</v>
       </c>
@@ -48782,7 +48785,7 @@
     </row>
     <row r="1935" spans="1:4" ht="69" x14ac:dyDescent="0.3">
       <c r="A1935" s="2" t="s">
-        <v>7017</v>
+        <v>7016</v>
       </c>
       <c r="B1935" s="2" t="s">
         <v>916</v>
@@ -48796,7 +48799,7 @@
     </row>
     <row r="1936" spans="1:4" ht="69" x14ac:dyDescent="0.3">
       <c r="A1936" s="2" t="s">
-        <v>7018</v>
+        <v>7017</v>
       </c>
       <c r="B1936" s="2" t="s">
         <v>928</v>
@@ -48810,7 +48813,7 @@
     </row>
     <row r="1937" spans="1:4" ht="110.4" x14ac:dyDescent="0.3">
       <c r="A1937" s="2" t="s">
-        <v>7019</v>
+        <v>7018</v>
       </c>
       <c r="B1937" s="2" t="s">
         <v>912</v>
@@ -48824,7 +48827,7 @@
     </row>
     <row r="1938" spans="1:4" ht="110.4" x14ac:dyDescent="0.3">
       <c r="A1938" s="2" t="s">
-        <v>7020</v>
+        <v>7019</v>
       </c>
       <c r="B1938" s="2" t="s">
         <v>924</v>
@@ -49468,7 +49471,7 @@
     </row>
     <row r="1984" spans="1:4" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A1984" s="2" t="s">
-        <v>7021</v>
+        <v>7020</v>
       </c>
       <c r="B1984" s="2" t="s">
         <v>6754</v>
@@ -49990,16 +49993,16 @@
     </row>
     <row r="2030" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2030" s="2" t="s">
+        <v>7022</v>
+      </c>
+      <c r="B2030" s="2" t="s">
         <v>7023</v>
       </c>
-      <c r="B2030" s="2">
-        <v>12345</v>
-      </c>
-      <c r="C2030" s="2">
-        <v>12345</v>
-      </c>
-      <c r="D2030" s="2">
-        <v>12345</v>
+      <c r="C2030" s="2" t="s">
+        <v>7023</v>
+      </c>
+      <c r="D2030" s="2" t="s">
+        <v>7023</v>
       </c>
     </row>
   </sheetData>
